--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/23.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/23.xlsx
@@ -426,13 +426,13 @@
         <v>-9.476764205136153</v>
       </c>
       <c r="E2">
-        <v>-12.90012559966391</v>
+        <v>-24.39953777035969</v>
       </c>
       <c r="F2">
-        <v>-1.574246126875744</v>
+        <v>-2.06504470099302</v>
       </c>
       <c r="G2">
-        <v>-12.13237257389551</v>
+        <v>-15.51270275786176</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.956682943706218</v>
       </c>
       <c r="E3">
-        <v>-12.67974288360663</v>
+        <v>-24.49537386578401</v>
       </c>
       <c r="F3">
-        <v>-1.462839823240641</v>
+        <v>-2.45434258887787</v>
       </c>
       <c r="G3">
-        <v>-12.66293384420126</v>
+        <v>-15.63084123070342</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.301038673104106</v>
       </c>
       <c r="E4">
-        <v>-13.18842636888824</v>
+        <v>-24.52870343448047</v>
       </c>
       <c r="F4">
-        <v>-1.701954700997941</v>
+        <v>-2.479601167724033</v>
       </c>
       <c r="G4">
-        <v>-12.15653293524111</v>
+        <v>-15.25496685599288</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.562996206635841</v>
       </c>
       <c r="E5">
-        <v>-14.32179472963194</v>
+        <v>-24.54705281115955</v>
       </c>
       <c r="F5">
-        <v>-0.7788899934452017</v>
+        <v>-2.328037269136016</v>
       </c>
       <c r="G5">
-        <v>-13.66264245451376</v>
+        <v>-14.80360542189588</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.753155669167158</v>
       </c>
       <c r="E6">
-        <v>-14.45514923220982</v>
+        <v>-24.78367010653433</v>
       </c>
       <c r="F6">
-        <v>-1.26452866701044</v>
+        <v>-2.373987637336707</v>
       </c>
       <c r="G6">
-        <v>-12.60050688696723</v>
+        <v>-14.78178396097377</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.907027418200504</v>
       </c>
       <c r="E7">
-        <v>-14.64206199687641</v>
+        <v>-25.57453639265591</v>
       </c>
       <c r="F7">
-        <v>-0.6989003519286731</v>
+        <v>-2.319342724876232</v>
       </c>
       <c r="G7">
-        <v>-12.00364201060095</v>
+        <v>-15.06017435646216</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.050154054237977</v>
       </c>
       <c r="E8">
-        <v>-15.01903934411894</v>
+        <v>-25.69837657134367</v>
       </c>
       <c r="F8">
-        <v>-0.8488920091861767</v>
+        <v>-1.805949601480197</v>
       </c>
       <c r="G8">
-        <v>-12.02333975655961</v>
+        <v>-14.66099208588238</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.206386965827164</v>
       </c>
       <c r="E9">
-        <v>-15.09220137018686</v>
+        <v>-26.41504833932357</v>
       </c>
       <c r="F9">
-        <v>-0.8778765846101314</v>
+        <v>-2.000228265193571</v>
       </c>
       <c r="G9">
-        <v>-11.57211571010249</v>
+        <v>-14.79788645447679</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.394372018382346</v>
       </c>
       <c r="E10">
-        <v>-16.08653199347307</v>
+        <v>-26.0336149736575</v>
       </c>
       <c r="F10">
-        <v>-0.3128629181412418</v>
+        <v>-1.997240343971673</v>
       </c>
       <c r="G10">
-        <v>-10.38041201123996</v>
+        <v>-14.06238089674414</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.636590491357335</v>
       </c>
       <c r="E11">
-        <v>-16.90275320556359</v>
+        <v>-27.53907898666346</v>
       </c>
       <c r="F11">
-        <v>-0.1807523996405683</v>
+        <v>-1.904775489368983</v>
       </c>
       <c r="G11">
-        <v>-10.5116950051453</v>
+        <v>-13.77236883114013</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.942576149495779</v>
       </c>
       <c r="E12">
-        <v>-18.70430696308707</v>
+        <v>-28.21407067987677</v>
       </c>
       <c r="F12">
-        <v>-0.2429868142454923</v>
+        <v>-1.921442241513309</v>
       </c>
       <c r="G12">
-        <v>-10.72075595595027</v>
+        <v>-13.65504806304667</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.315594679378469</v>
       </c>
       <c r="E13">
-        <v>-18.12427284134061</v>
+        <v>-28.6972045148071</v>
       </c>
       <c r="F13">
-        <v>-0.5699227189453873</v>
+        <v>-1.913710260175579</v>
       </c>
       <c r="G13">
-        <v>-9.751160067862987</v>
+        <v>-12.75924754557528</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.7675766866430197</v>
       </c>
       <c r="E14">
-        <v>-19.09543126312956</v>
+        <v>-28.71155977741142</v>
       </c>
       <c r="F14">
-        <v>-0.2933540374379107</v>
+        <v>-1.991535377668592</v>
       </c>
       <c r="G14">
-        <v>-8.908010466648166</v>
+        <v>-13.4375154262067</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.2981602718874803</v>
       </c>
       <c r="E15">
-        <v>-21.32611680304191</v>
+        <v>-29.70902636894793</v>
       </c>
       <c r="F15">
-        <v>0.007774909195168407</v>
+        <v>-1.130533612668397</v>
       </c>
       <c r="G15">
-        <v>-8.600775287876102</v>
+        <v>-11.91726656693582</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.09874956976212305</v>
       </c>
       <c r="E16">
-        <v>-21.30411747631264</v>
+        <v>-30.20808684696324</v>
       </c>
       <c r="F16">
-        <v>0.4975239418130977</v>
+        <v>-1.516315080928364</v>
       </c>
       <c r="G16">
-        <v>-8.724768460503967</v>
+        <v>-11.89711196569274</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.4274305221293747</v>
       </c>
       <c r="E17">
-        <v>-21.72712676184314</v>
+        <v>-31.83874958085927</v>
       </c>
       <c r="F17">
-        <v>0.5081303580385426</v>
+        <v>-1.533406785550326</v>
       </c>
       <c r="G17">
-        <v>-6.60813806451554</v>
+        <v>-12.04586801895435</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.6985911166006019</v>
       </c>
       <c r="E18">
-        <v>-22.19809711558887</v>
+        <v>-31.64194210048592</v>
       </c>
       <c r="F18">
-        <v>0.4075002859464587</v>
+        <v>-1.443963815233049</v>
       </c>
       <c r="G18">
-        <v>-6.529297422497796</v>
+        <v>-11.44095189583656</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.923744593744474</v>
       </c>
       <c r="E19">
-        <v>-23.59557513740793</v>
+        <v>-32.71770827185205</v>
       </c>
       <c r="F19">
-        <v>0.674608183346562</v>
+        <v>-1.266887857373613</v>
       </c>
       <c r="G19">
-        <v>-6.640333119884952</v>
+        <v>-10.37830319373144</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.112636073745071</v>
       </c>
       <c r="E20">
-        <v>-24.82117492826586</v>
+        <v>-33.91088645305207</v>
       </c>
       <c r="F20">
-        <v>0.6607065215927808</v>
+        <v>-1.002055485229</v>
       </c>
       <c r="G20">
-        <v>-5.611279833912358</v>
+        <v>-10.68962027515343</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.273938099375037</v>
       </c>
       <c r="E21">
-        <v>-25.0719980466027</v>
+        <v>-33.45790999077582</v>
       </c>
       <c r="F21">
-        <v>0.7523703449169629</v>
+        <v>-0.8241702124170283</v>
       </c>
       <c r="G21">
-        <v>-5.729320645660611</v>
+        <v>-10.41283218370604</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.415680775707855</v>
       </c>
       <c r="E22">
-        <v>-26.4958272586724</v>
+        <v>-34.56176855064854</v>
       </c>
       <c r="F22">
-        <v>0.8547780934554545</v>
+        <v>-1.050657457486052</v>
       </c>
       <c r="G22">
-        <v>-5.459077502744364</v>
+        <v>-10.10480909509563</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.545449423902091</v>
       </c>
       <c r="E23">
-        <v>-25.62068154279407</v>
+        <v>-34.68327656522235</v>
       </c>
       <c r="F23">
-        <v>1.207261677225089</v>
+        <v>-0.8366263730529244</v>
       </c>
       <c r="G23">
-        <v>-5.272048232503239</v>
+        <v>-9.935408479851125</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.67058263506131</v>
       </c>
       <c r="E24">
-        <v>-27.5527368642706</v>
+        <v>-35.45669237675536</v>
       </c>
       <c r="F24">
-        <v>1.189907380136439</v>
+        <v>-0.527706630996516</v>
       </c>
       <c r="G24">
-        <v>-4.988178884147352</v>
+        <v>-9.551183254017772</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.79799268824385</v>
       </c>
       <c r="E25">
-        <v>-27.29411118521853</v>
+        <v>-35.71858534980396</v>
       </c>
       <c r="F25">
-        <v>1.070673832912284</v>
+        <v>-0.5742161471940971</v>
       </c>
       <c r="G25">
-        <v>-3.586867994465869</v>
+        <v>-10.41096172547635</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.933697114136564</v>
       </c>
       <c r="E26">
-        <v>-28.0457699433817</v>
+        <v>-35.0584425228618</v>
       </c>
       <c r="F26">
-        <v>1.062438204193651</v>
+        <v>-0.3829817336860116</v>
       </c>
       <c r="G26">
-        <v>-4.241217183576055</v>
+        <v>-9.440793113010773</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.085536477042015</v>
       </c>
       <c r="E27">
-        <v>-27.50909143178467</v>
+        <v>-35.82403086707257</v>
       </c>
       <c r="F27">
-        <v>1.102029195843051</v>
+        <v>-0.4898013670118134</v>
       </c>
       <c r="G27">
-        <v>-4.342410629074958</v>
+        <v>-10.00858477845117</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.257620288609904</v>
       </c>
       <c r="E28">
-        <v>-27.7625003087799</v>
+        <v>-35.88443391762387</v>
       </c>
       <c r="F28">
-        <v>1.42595398503377</v>
+        <v>-0.6784305650380944</v>
       </c>
       <c r="G28">
-        <v>-3.884893235547679</v>
+        <v>-10.32141477918461</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.447495431857417</v>
       </c>
       <c r="E29">
-        <v>-27.21124011087817</v>
+        <v>-35.39057439200637</v>
       </c>
       <c r="F29">
-        <v>1.154903887163743</v>
+        <v>-0.5659631227600056</v>
       </c>
       <c r="G29">
-        <v>-4.399322217440568</v>
+        <v>-10.02243610098749</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.653429058738338</v>
       </c>
       <c r="E30">
-        <v>-26.70432273045954</v>
+        <v>-35.40415302131837</v>
       </c>
       <c r="F30">
-        <v>1.383853040153888</v>
+        <v>-0.5878386491331349</v>
       </c>
       <c r="G30">
-        <v>-4.679212290058251</v>
+        <v>-9.88378383271173</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.867893330940927</v>
       </c>
       <c r="E31">
-        <v>-27.39697094382876</v>
+        <v>-36.10658726701816</v>
       </c>
       <c r="F31">
-        <v>1.386200633373421</v>
+        <v>-0.2659052551787462</v>
       </c>
       <c r="G31">
-        <v>-4.022684761983225</v>
+        <v>-10.23217571362801</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.076850058461265</v>
       </c>
       <c r="E32">
-        <v>-26.90747913139165</v>
+        <v>-35.00496577330523</v>
       </c>
       <c r="F32">
-        <v>1.271274596643823</v>
+        <v>-0.7125708991770733</v>
       </c>
       <c r="G32">
-        <v>-4.80403640961647</v>
+        <v>-10.53840779710167</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.26556644323352</v>
       </c>
       <c r="E33">
-        <v>-26.83503260421694</v>
+        <v>-34.44827819930531</v>
       </c>
       <c r="F33">
-        <v>1.216053968838403</v>
+        <v>-0.4669856436365066</v>
       </c>
       <c r="G33">
-        <v>-4.281155604961823</v>
+        <v>-10.26557249702818</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.415992059724169</v>
       </c>
       <c r="E34">
-        <v>-27.07032305670748</v>
+        <v>-34.48459882508383</v>
       </c>
       <c r="F34">
-        <v>1.606324360054139</v>
+        <v>-0.3647145757194769</v>
       </c>
       <c r="G34">
-        <v>-4.50628925435996</v>
+        <v>-10.99883516015797</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.507515695960731</v>
       </c>
       <c r="E35">
-        <v>-27.22556820263843</v>
+        <v>-34.70408037481359</v>
       </c>
       <c r="F35">
-        <v>1.60701687520288</v>
+        <v>-0.4721223499012664</v>
       </c>
       <c r="G35">
-        <v>-5.155321707334076</v>
+        <v>-10.9869171962166</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.520006475138822</v>
       </c>
       <c r="E36">
-        <v>-26.42261089091638</v>
+        <v>-33.88151929911233</v>
       </c>
       <c r="F36">
-        <v>1.367535859053543</v>
+        <v>-0.4698360558695397</v>
       </c>
       <c r="G36">
-        <v>-5.292831837398783</v>
+        <v>-10.93007181876177</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.435795256481188</v>
       </c>
       <c r="E37">
-        <v>-25.15058065605781</v>
+        <v>-33.7003101474584</v>
       </c>
       <c r="F37">
-        <v>2.094950126473873</v>
+        <v>-0.2675520495755117</v>
       </c>
       <c r="G37">
-        <v>-5.399120212482623</v>
+        <v>-10.72733069939126</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.240781393050154</v>
       </c>
       <c r="E38">
-        <v>-24.74662266067758</v>
+        <v>-32.69324092678861</v>
       </c>
       <c r="F38">
-        <v>1.741850237356555</v>
+        <v>-0.4454472627963167</v>
       </c>
       <c r="G38">
-        <v>-6.096688573607995</v>
+        <v>-10.45653469536996</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.926589391343904</v>
       </c>
       <c r="E39">
-        <v>-23.74903606457986</v>
+        <v>-32.66897962729252</v>
       </c>
       <c r="F39">
-        <v>1.844311001408826</v>
+        <v>-0.1356395108841072</v>
       </c>
       <c r="G39">
-        <v>-5.934203687995026</v>
+        <v>-11.06601275024086</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.489386078768173</v>
       </c>
       <c r="E40">
-        <v>-24.18875994767267</v>
+        <v>-31.63065261478479</v>
       </c>
       <c r="F40">
-        <v>1.62384764409296</v>
+        <v>-0.3061746797310386</v>
       </c>
       <c r="G40">
-        <v>-5.570301901227259</v>
+        <v>-10.68390958409818</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.930342989468505</v>
       </c>
       <c r="E41">
-        <v>-24.11568396261089</v>
+        <v>-32.6198479485463</v>
       </c>
       <c r="F41">
-        <v>2.105644349644014</v>
+        <v>0.02268635081296231</v>
       </c>
       <c r="G41">
-        <v>-6.524394504554136</v>
+        <v>-9.968282197056087</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.259953197576234</v>
       </c>
       <c r="E42">
-        <v>-21.89841629118327</v>
+        <v>-31.83666874705274</v>
       </c>
       <c r="F42">
-        <v>2.170644683006886</v>
+        <v>-0.08691328351663469</v>
       </c>
       <c r="G42">
-        <v>-6.008005679701999</v>
+        <v>-10.35112692539957</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.4862650526390407</v>
       </c>
       <c r="E43">
-        <v>-21.64628444385821</v>
+        <v>-30.37766234889147</v>
       </c>
       <c r="F43">
-        <v>2.533911953626165</v>
+        <v>0.2105269430717782</v>
       </c>
       <c r="G43">
-        <v>-6.78701677163898</v>
+        <v>-11.56027388870851</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.3783104203861786</v>
       </c>
       <c r="E44">
-        <v>-20.04487565205173</v>
+        <v>-29.62199136275751</v>
       </c>
       <c r="F44">
-        <v>1.777060822179951</v>
+        <v>0.04752411901850268</v>
       </c>
       <c r="G44">
-        <v>-7.52483474543081</v>
+        <v>-11.28446571874075</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.312148941831428</v>
       </c>
       <c r="E45">
-        <v>-21.31183852449572</v>
+        <v>-30.00702033678568</v>
       </c>
       <c r="F45">
-        <v>2.148626677440475</v>
+        <v>0.01325290282988154</v>
       </c>
       <c r="G45">
-        <v>-6.317412576347823</v>
+        <v>-11.21422587403404</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.299759270245537</v>
       </c>
       <c r="E46">
-        <v>-20.67381729308104</v>
+        <v>-29.18052854564576</v>
       </c>
       <c r="F46">
-        <v>1.717935270437734</v>
+        <v>0.09482555445316006</v>
       </c>
       <c r="G46">
-        <v>-7.523821718495793</v>
+        <v>-11.24290844058628</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.323376444383573</v>
       </c>
       <c r="E47">
-        <v>-19.8735272525495</v>
+        <v>-28.48460171709499</v>
       </c>
       <c r="F47">
-        <v>1.968547887745891</v>
+        <v>-0.1368207628004993</v>
       </c>
       <c r="G47">
-        <v>-6.794247003096748</v>
+        <v>-11.56480933609731</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.359760870955925</v>
       </c>
       <c r="E48">
-        <v>-19.61762771485006</v>
+        <v>-27.41071033396803</v>
       </c>
       <c r="F48">
-        <v>2.023968980462789</v>
+        <v>-0.007131562218208696</v>
       </c>
       <c r="G48">
-        <v>-7.315290454977101</v>
+        <v>-11.45380674416555</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.388987716675523</v>
       </c>
       <c r="E49">
-        <v>-17.51745732431278</v>
+        <v>-27.10605724510201</v>
       </c>
       <c r="F49">
-        <v>2.062600722659746</v>
+        <v>0.01931655221837392</v>
       </c>
       <c r="G49">
-        <v>-7.846030494741979</v>
+        <v>-10.73331947627181</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.394387156357304</v>
       </c>
       <c r="E50">
-        <v>-17.34668856948353</v>
+        <v>-27.02612515039262</v>
       </c>
       <c r="F50">
-        <v>2.190494022712768</v>
+        <v>0.1763451905626594</v>
       </c>
       <c r="G50">
-        <v>-7.51633988557704</v>
+        <v>-11.43137117704591</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.356059190952933</v>
       </c>
       <c r="E51">
-        <v>-17.51470854059012</v>
+        <v>-26.21268442134281</v>
       </c>
       <c r="F51">
-        <v>2.173119844806451</v>
+        <v>0.05130810131449082</v>
       </c>
       <c r="G51">
-        <v>-7.466711497397826</v>
+        <v>-11.47302446102102</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.251819627949045</v>
       </c>
       <c r="E52">
-        <v>-15.9671750040529</v>
+        <v>-26.12105980674561</v>
       </c>
       <c r="F52">
-        <v>2.132775038820504</v>
+        <v>-0.04513705865865001</v>
       </c>
       <c r="G52">
-        <v>-7.592373184977482</v>
+        <v>-11.85634921846769</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.069220424139123</v>
       </c>
       <c r="E53">
-        <v>-16.19393381151298</v>
+        <v>-25.30267851255343</v>
       </c>
       <c r="F53">
-        <v>1.881145186341709</v>
+        <v>0.03554592637402183</v>
       </c>
       <c r="G53">
-        <v>-7.362326685999066</v>
+        <v>-11.75351374238131</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.794053209099813</v>
       </c>
       <c r="E54">
-        <v>-15.53824247452037</v>
+        <v>-25.36779344030973</v>
       </c>
       <c r="F54">
-        <v>2.126767718415402</v>
+        <v>0.157626572361599</v>
       </c>
       <c r="G54">
-        <v>-8.943473030464839</v>
+        <v>-11.45450526927434</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.40514456472173</v>
       </c>
       <c r="E55">
-        <v>-14.44259177378655</v>
+        <v>-23.62640951692616</v>
       </c>
       <c r="F55">
-        <v>2.127042736393131</v>
+        <v>-0.08917803999588853</v>
       </c>
       <c r="G55">
-        <v>-8.197699815742139</v>
+        <v>-12.02862669778582</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.89806174109969</v>
       </c>
       <c r="E56">
-        <v>-13.57592788972459</v>
+        <v>-24.88295689915251</v>
       </c>
       <c r="F56">
-        <v>1.8886286574586</v>
+        <v>0.2779038625132816</v>
       </c>
       <c r="G56">
-        <v>-7.696397146912461</v>
+        <v>-12.04017719117234</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.26776519489392</v>
       </c>
       <c r="E57">
-        <v>-13.97139499634043</v>
+        <v>-23.93671414135375</v>
       </c>
       <c r="F57">
-        <v>2.096146289003515</v>
+        <v>0.06751593791766596</v>
       </c>
       <c r="G57">
-        <v>-8.112294361920021</v>
+        <v>-12.43650246095173</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.50423486161873</v>
       </c>
       <c r="E58">
-        <v>-11.87081704314246</v>
+        <v>-23.82518688349285</v>
       </c>
       <c r="F58">
-        <v>2.148608453357614</v>
+        <v>-0.1490317266851668</v>
       </c>
       <c r="G58">
-        <v>-8.369613135050953</v>
+        <v>-11.98050129728144</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.61093875256465</v>
       </c>
       <c r="E59">
-        <v>-11.96489156217781</v>
+        <v>-22.93927698489829</v>
       </c>
       <c r="F59">
-        <v>1.996291568800452</v>
+        <v>0.1038232811823683</v>
       </c>
       <c r="G59">
-        <v>-7.847761910059018</v>
+        <v>-12.03237092479074</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.59596792528672</v>
       </c>
       <c r="E60">
-        <v>-12.66064630871628</v>
+        <v>-22.63762174582534</v>
       </c>
       <c r="F60">
-        <v>1.660496274727616</v>
+        <v>-0.1231038269775423</v>
       </c>
       <c r="G60">
-        <v>-8.704233146523867</v>
+        <v>-12.82987472411009</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.46195227394069</v>
       </c>
       <c r="E61">
-        <v>-11.60269968257032</v>
+        <v>-22.64541977806655</v>
       </c>
       <c r="F61">
-        <v>1.455539955192157</v>
+        <v>-0.01156332782318605</v>
       </c>
       <c r="G61">
-        <v>-8.293967169478606</v>
+        <v>-12.39603104173414</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.21515760980031</v>
       </c>
       <c r="E62">
-        <v>-10.95720646904298</v>
+        <v>-22.26249201597794</v>
       </c>
       <c r="F62">
-        <v>1.405587744068541</v>
+        <v>-0.3290964341339037</v>
       </c>
       <c r="G62">
-        <v>-8.121057375962472</v>
+        <v>-11.94670393787102</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.87554687818745</v>
       </c>
       <c r="E63">
-        <v>-10.56055290223713</v>
+        <v>-21.67907965262176</v>
       </c>
       <c r="F63">
-        <v>0.8009921979916826</v>
+        <v>-0.3172433249672456</v>
       </c>
       <c r="G63">
-        <v>-8.223330059307177</v>
+        <v>-11.84730811859994</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.45540395082329</v>
       </c>
       <c r="E64">
-        <v>-11.43615146551622</v>
+        <v>-22.1885465639067</v>
       </c>
       <c r="F64">
-        <v>0.9095762538854474</v>
+        <v>-0.1613661173128514</v>
       </c>
       <c r="G64">
-        <v>-7.522868281380483</v>
+        <v>-12.25112184238916</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.962145386204224</v>
       </c>
       <c r="E65">
-        <v>-8.726964719583385</v>
+        <v>-22.28139386648596</v>
       </c>
       <c r="F65">
-        <v>1.332093331357363</v>
+        <v>-0.1596886733221825</v>
       </c>
       <c r="G65">
-        <v>-7.979349474153969</v>
+        <v>-11.91436321849788</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.420469998944956</v>
       </c>
       <c r="E66">
-        <v>-11.37956365431637</v>
+        <v>-21.92554637896323</v>
       </c>
       <c r="F66">
-        <v>0.8632688593341494</v>
+        <v>-0.5526380047185727</v>
       </c>
       <c r="G66">
-        <v>-7.161601688861976</v>
+        <v>-12.59591184975872</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.844665580151537</v>
       </c>
       <c r="E67">
-        <v>-10.83576638157929</v>
+        <v>-21.64788299518292</v>
       </c>
       <c r="F67">
-        <v>0.9312894202476281</v>
+        <v>-0.5576347168922593</v>
       </c>
       <c r="G67">
-        <v>-7.660507522721222</v>
+        <v>-12.54930598965686</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.239981681868707</v>
       </c>
       <c r="E68">
-        <v>-9.386686398442826</v>
+        <v>-22.05478902714214</v>
       </c>
       <c r="F68">
-        <v>0.6889000061470619</v>
+        <v>-0.6316642549456456</v>
       </c>
       <c r="G68">
-        <v>-7.407571911884285</v>
+        <v>-11.9245232827579</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.622898767704575</v>
       </c>
       <c r="E69">
-        <v>-9.534368992780973</v>
+        <v>-21.73012914011023</v>
       </c>
       <c r="F69">
-        <v>0.6523449810289225</v>
+        <v>-0.6820538440579395</v>
       </c>
       <c r="G69">
-        <v>-8.373311014418318</v>
+        <v>-12.57738272637542</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.002326131294954</v>
       </c>
       <c r="E70">
-        <v>-10.03697526594429</v>
+        <v>-21.83575579633914</v>
       </c>
       <c r="F70">
-        <v>0.4895956374009037</v>
+        <v>-1.161317402091233</v>
       </c>
       <c r="G70">
-        <v>-7.659524290696059</v>
+        <v>-11.44289187552257</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.377050009133085</v>
       </c>
       <c r="E71">
-        <v>-9.451384706590412</v>
+        <v>-21.08685940732065</v>
       </c>
       <c r="F71">
-        <v>0.4828933167448529</v>
+        <v>-1.149509853131728</v>
       </c>
       <c r="G71">
-        <v>-7.55299755633339</v>
+        <v>-11.38301734889932</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.748108568238627</v>
       </c>
       <c r="E72">
-        <v>-8.848708214805596</v>
+        <v>-21.11355929006988</v>
       </c>
       <c r="F72">
-        <v>0.2967359670485256</v>
+        <v>-1.033854024720264</v>
       </c>
       <c r="G72">
-        <v>-7.474881923788747</v>
+        <v>-11.9405397020769</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.117882448686015</v>
       </c>
       <c r="E73">
-        <v>-9.60442901415364</v>
+        <v>-21.51708708041938</v>
       </c>
       <c r="F73">
-        <v>0.04435478533539178</v>
+        <v>-1.132928422829891</v>
       </c>
       <c r="G73">
-        <v>-7.201500383701272</v>
+        <v>-11.86638679254276</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.480327600105324</v>
       </c>
       <c r="E74">
-        <v>-8.767403992471882</v>
+        <v>-21.8921760540007</v>
       </c>
       <c r="F74">
-        <v>0.007058371391746835</v>
+        <v>-1.365259799925665</v>
       </c>
       <c r="G74">
-        <v>-6.232629505087088</v>
+        <v>-11.48508146787505</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.827529441573899</v>
       </c>
       <c r="E75">
-        <v>-10.36732291632983</v>
+        <v>-21.6985883186468</v>
       </c>
       <c r="F75">
-        <v>-0.3531091484062558</v>
+        <v>-1.204859706251986</v>
       </c>
       <c r="G75">
-        <v>-6.80991250458858</v>
+        <v>-10.82161172580417</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.160503531030385</v>
       </c>
       <c r="E76">
-        <v>-10.17354951354162</v>
+        <v>-21.50515002293515</v>
       </c>
       <c r="F76">
-        <v>-0.1763115219941601</v>
+        <v>-1.595184769716307</v>
       </c>
       <c r="G76">
-        <v>-6.522573704507537</v>
+        <v>-10.89465891312819</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.472081356596664</v>
       </c>
       <c r="E77">
-        <v>-10.75491500664634</v>
+        <v>-21.73950760978011</v>
       </c>
       <c r="F77">
-        <v>0.01005871812468664</v>
+        <v>-1.465400306882695</v>
       </c>
       <c r="G77">
-        <v>-5.987731898819502</v>
+        <v>-11.28194970413091</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.755502150774125</v>
       </c>
       <c r="E78">
-        <v>-11.47654545366464</v>
+        <v>-22.09185911536893</v>
       </c>
       <c r="F78">
-        <v>-0.6803730865976593</v>
+        <v>-1.232684567312021</v>
       </c>
       <c r="G78">
-        <v>-5.826468604510524</v>
+        <v>-10.51741231729162</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.009911932669797</v>
       </c>
       <c r="E79">
-        <v>-11.46175545755559</v>
+        <v>-22.08327765712439</v>
       </c>
       <c r="F79">
-        <v>-0.6344268602339819</v>
+        <v>-1.796192261842621</v>
       </c>
       <c r="G79">
-        <v>-5.122113625029646</v>
+        <v>-10.91083423863307</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.2319697791898279</v>
       </c>
       <c r="E80">
-        <v>-11.61287063519155</v>
+        <v>-23.02687578610266</v>
       </c>
       <c r="F80">
-        <v>-0.3380825637194728</v>
+        <v>-1.593806366358049</v>
       </c>
       <c r="G80">
-        <v>-5.476315513367349</v>
+        <v>-10.7453400671249</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.5747486240817395</v>
       </c>
       <c r="E81">
-        <v>-12.96913048659279</v>
+        <v>-23.36160699932763</v>
       </c>
       <c r="F81">
-        <v>-0.1992150523141636</v>
+        <v>-1.711311939179964</v>
       </c>
       <c r="G81">
-        <v>-4.924728968341681</v>
+        <v>-10.38876782818108</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.40783336235103</v>
       </c>
       <c r="E82">
-        <v>-12.43652307312866</v>
+        <v>-22.79479149320956</v>
       </c>
       <c r="F82">
-        <v>-0.6863613545524969</v>
+        <v>-1.790598296771516</v>
       </c>
       <c r="G82">
-        <v>-4.990370465294349</v>
+        <v>-10.54106285462417</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.260834211334165</v>
       </c>
       <c r="E83">
-        <v>-13.57968199467695</v>
+        <v>-24.57832645265652</v>
       </c>
       <c r="F83">
-        <v>-0.6662784152390258</v>
+        <v>-1.722497384219966</v>
       </c>
       <c r="G83">
-        <v>-4.378032099077515</v>
+        <v>-10.75187177347388</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.121026948284402</v>
       </c>
       <c r="E84">
-        <v>-14.69044421317436</v>
+        <v>-25.17346756369258</v>
       </c>
       <c r="F84">
-        <v>-0.1213907631885529</v>
+        <v>-1.822794452616125</v>
       </c>
       <c r="G84">
-        <v>-3.164273545832363</v>
+        <v>-10.41387500555091</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.977617593838247</v>
       </c>
       <c r="E85">
-        <v>-15.64237020585274</v>
+        <v>-26.16579660146739</v>
       </c>
       <c r="F85">
-        <v>-0.5320679853722554</v>
+        <v>-1.79150784417979</v>
       </c>
       <c r="G85">
-        <v>-4.686631222611758</v>
+        <v>-10.57411534128825</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.817435244740376</v>
       </c>
       <c r="E86">
-        <v>-17.84378821825352</v>
+        <v>-26.42298222578501</v>
       </c>
       <c r="F86">
-        <v>-0.584165668069122</v>
+        <v>-2.078989437851747</v>
       </c>
       <c r="G86">
-        <v>-4.464467132562347</v>
+        <v>-10.15939336994714</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.623403331957589</v>
       </c>
       <c r="E87">
-        <v>-17.52112085978498</v>
+        <v>-26.90822632960292</v>
       </c>
       <c r="F87">
-        <v>-0.4031466813723599</v>
+        <v>-2.030006416589407</v>
       </c>
       <c r="G87">
-        <v>-3.891547432081614</v>
+        <v>-10.11138714908216</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>6.379406819002208</v>
       </c>
       <c r="E88">
-        <v>-19.91129925424748</v>
+        <v>-28.30204534442378</v>
       </c>
       <c r="F88">
-        <v>-0.2670351483161648</v>
+        <v>-2.088943928931189</v>
       </c>
       <c r="G88">
-        <v>-4.206866963060577</v>
+        <v>-10.48826958490941</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>7.074135624865093</v>
       </c>
       <c r="E89">
-        <v>-20.12564551445254</v>
+        <v>-29.65887578354999</v>
       </c>
       <c r="F89">
-        <v>-0.6074535608640245</v>
+        <v>-1.826551927155223</v>
       </c>
       <c r="G89">
-        <v>-3.835092699000423</v>
+        <v>-10.28277409165023</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>7.695524119669717</v>
       </c>
       <c r="E90">
-        <v>-23.33178246951312</v>
+        <v>-30.74952252050533</v>
       </c>
       <c r="F90">
-        <v>-0.3210380760394702</v>
+        <v>-2.209881427902903</v>
       </c>
       <c r="G90">
-        <v>-3.747651259671653</v>
+        <v>-10.51853459222943</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>8.228500989365344</v>
       </c>
       <c r="E91">
-        <v>-24.37883811567063</v>
+        <v>-31.96109083465049</v>
       </c>
       <c r="F91">
-        <v>-0.07282275399501509</v>
+        <v>-1.932800815340496</v>
       </c>
       <c r="G91">
-        <v>-4.355493905046157</v>
+        <v>-9.832394234305623</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>8.669586052306727</v>
       </c>
       <c r="E92">
-        <v>-25.83582481442448</v>
+        <v>-33.8569432706727</v>
       </c>
       <c r="F92">
-        <v>-0.4649014712510631</v>
+        <v>-2.398767419824052</v>
       </c>
       <c r="G92">
-        <v>-3.955964027184753</v>
+        <v>-10.57487014567121</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>9.015020531942044</v>
       </c>
       <c r="E93">
-        <v>-26.93245366554396</v>
+        <v>-34.6263332688129</v>
       </c>
       <c r="F93">
-        <v>0.3585735936675086</v>
+        <v>-2.136753981951165</v>
       </c>
       <c r="G93">
-        <v>-3.954474281692081</v>
+        <v>-10.58680135179474</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>9.254527135636543</v>
       </c>
       <c r="E94">
-        <v>-30.38199609851681</v>
+        <v>-35.96138854067322</v>
       </c>
       <c r="F94">
-        <v>0.1544100217365285</v>
+        <v>-2.37820485578436</v>
       </c>
       <c r="G94">
-        <v>-5.107136717009984</v>
+        <v>-10.25421401528294</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>9.39674096541572</v>
       </c>
       <c r="E95">
-        <v>-32.06401625613383</v>
+        <v>-37.32066209152656</v>
       </c>
       <c r="F95">
-        <v>0.3324013255760583</v>
+        <v>-2.235270888798708</v>
       </c>
       <c r="G95">
-        <v>-4.908391426105378</v>
+        <v>-10.50878172507074</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>9.444347448784773</v>
       </c>
       <c r="E96">
-        <v>-33.47013007788551</v>
+        <v>-39.82235642266495</v>
       </c>
       <c r="F96">
-        <v>0.4519496524132773</v>
+        <v>-2.447889606810063</v>
       </c>
       <c r="G96">
-        <v>-4.915240944826129</v>
+        <v>-10.32512259018859</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>9.404870337589827</v>
       </c>
       <c r="E97">
-        <v>-35.81503958193034</v>
+        <v>-40.39363247568058</v>
       </c>
       <c r="F97">
-        <v>0.5185296824132876</v>
+        <v>-2.391910194463677</v>
       </c>
       <c r="G97">
-        <v>-4.965908844304675</v>
+        <v>-10.74661462715752</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>9.27260542199315</v>
       </c>
       <c r="E98">
-        <v>-38.5929640348256</v>
+        <v>-42.43568669504043</v>
       </c>
       <c r="F98">
-        <v>0.2542995333705097</v>
+        <v>-2.251617891125553</v>
       </c>
       <c r="G98">
-        <v>-5.343420283784386</v>
+        <v>-11.36528275644544</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>9.080445671611818</v>
       </c>
       <c r="E99">
-        <v>-40.15734349467136</v>
+        <v>-44.29539511577041</v>
       </c>
       <c r="F99">
-        <v>0.695894740496301</v>
+        <v>-2.87711231840764</v>
       </c>
       <c r="G99">
-        <v>-5.601762015486952</v>
+        <v>-11.10181630024808</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>8.798159437496439</v>
       </c>
       <c r="E100">
-        <v>-43.09126255594585</v>
+        <v>-46.07480689963339</v>
       </c>
       <c r="F100">
-        <v>0.9445863737973657</v>
+        <v>-2.889871661512961</v>
       </c>
       <c r="G100">
-        <v>-5.162068599143111</v>
+        <v>-11.36769283359803</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>8.473436118663757</v>
       </c>
       <c r="E101">
-        <v>-44.66116222560695</v>
+        <v>-48.16472482501731</v>
       </c>
       <c r="F101">
-        <v>0.7899152690814476</v>
+        <v>-2.815089965857833</v>
       </c>
       <c r="G101">
-        <v>-5.769947660518547</v>
+        <v>-12.28149609771198</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>8.03007442823497</v>
       </c>
       <c r="E102">
-        <v>-46.96181042470081</v>
+        <v>-50.03498345806666</v>
       </c>
       <c r="F102">
-        <v>0.9246657944948432</v>
+        <v>-2.86963795933218</v>
       </c>
       <c r="G102">
-        <v>-6.350753080473823</v>
+        <v>-11.5609558610896</v>
       </c>
     </row>
   </sheetData>
